--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -495,129 +495,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>沪深300ETF</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>510300</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>4.616</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>259900</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1199698.4</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>D2026090401</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>中国平安</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>601318</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>58.24</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>20600</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>1199744</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>D2026090403</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>紫金矿业</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>601899</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>35900</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1197265</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>D2026090402</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -629,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -675,87 +552,6 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>浮动盈亏%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>沪深300ETF</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>259900</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>4.616</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>4.616</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1199698</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>中国平安</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>20600</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>58.24</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>58.24</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1199744</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>紫金矿业</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>35900</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1197265</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -836,7 +632,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1403292.6</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="4">
@@ -846,7 +642,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3596707.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -878,7 +674,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>899.1799999999999</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -495,6 +495,129 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>4.634</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>258900</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1199742.6</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>D2026090701</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>601318</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>21200</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1194832</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>D2026090703</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>36500</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1199755</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>D2026090702</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -506,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -552,6 +675,87 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>浮动盈亏%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>258900</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>4.634</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4.634</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1199743</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1194832</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>36500</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1199755</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -632,7 +836,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5000000</v>
+        <v>1405670.4</v>
       </c>
     </row>
     <row r="4">
@@ -642,7 +846,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>3594329.6</v>
       </c>
     </row>
     <row r="5">
@@ -674,7 +878,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>898.58</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.634</v>
+        <v>4.638</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>258900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1199742.6</v>
+        <v>1200778.2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>56.36</v>
+        <v>56</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>21200</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1194832</v>
+        <v>1187200</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32.87</v>
+        <v>33.44</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>36500</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1199755</v>
+        <v>1220560</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>258900</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4.634</v>
+        <v>4.638</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.634</v>
+        <v>4.638</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1199743</v>
+        <v>1200778</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -715,13 +715,13 @@
         <v>21200</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>56.36</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>56.36</v>
+        <v>56</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1194832</v>
+        <v>1187200</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>36500</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>32.87</v>
+        <v>33.44</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.87</v>
+        <v>33.44</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1199755</v>
+        <v>1220560</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1405670.4</v>
+        <v>1391461.8</v>
       </c>
     </row>
     <row r="4">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3594329.6</v>
+        <v>3608538.2</v>
       </c>
     </row>
     <row r="5">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>898.58</v>
+        <v>902.13</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.638</v>
+        <v>4.641</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>258900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1200778.2</v>
+        <v>1201554.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>56</v>
+        <v>56.12</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>21200</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1187200</v>
+        <v>1189744</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33.44</v>
+        <v>33.75</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>36500</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1220560</v>
+        <v>1231875</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>258900</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4.638</v>
+        <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.638</v>
+        <v>4.641</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1200778</v>
+        <v>1201555</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -715,13 +715,13 @@
         <v>21200</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>56</v>
+        <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>56</v>
+        <v>56.12</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1187200</v>
+        <v>1189744</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>36500</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>33.44</v>
+        <v>33.75</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33.44</v>
+        <v>33.75</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1220560</v>
+        <v>1231875</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1391461.8</v>
+        <v>1376826.1</v>
       </c>
     </row>
     <row r="4">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3608538.2</v>
+        <v>3623173.9</v>
       </c>
     </row>
     <row r="5">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>902.13</v>
+        <v>905.79</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -544,12 +544,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -558,17 +558,17 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>56.12</v>
+        <v>27.87</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>21200</v>
+        <v>13500</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1189744</v>
+        <v>376245</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D2026090703</t>
+          <t>D2026090801</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -585,34 +585,75 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>601318</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>21200</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1189744</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>D2026090703</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>紫金矿业</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>601899</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>买入</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>33.75</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>36500</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>1231875</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>D2026090702</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
@@ -629,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -708,20 +749,20 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>21200</v>
+        <v>13500</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>56.12</v>
+        <v>27.87</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>56.12</v>
+        <v>27.87</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1189744</v>
+        <v>376245</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -735,20 +776,20 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>36500</v>
+        <v>21200</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>33.75</v>
+        <v>56.12</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33.75</v>
+        <v>56.12</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1231875</v>
+        <v>1189744</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -756,6 +797,33 @@
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>36500</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1235890</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4015</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
         </is>
       </c>
     </row>
@@ -836,7 +904,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1376826.1</v>
+        <v>1000581.1</v>
       </c>
     </row>
     <row r="4">
@@ -846,7 +914,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3623173.9</v>
+        <v>4003433.9</v>
       </c>
     </row>
     <row r="5">
@@ -856,7 +924,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5000000</v>
+        <v>5004015</v>
       </c>
     </row>
     <row r="6">
@@ -867,7 +935,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.08%</t>
         </is>
       </c>
     </row>
@@ -878,7 +946,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>905.79</v>
+        <v>999.85</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -732,17 +732,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.641</v>
+        <v>4.624</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1201555</v>
+        <v>1197154</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>-4401</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.37%</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
         <v>56.12</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>56.12</v>
+        <v>55.7</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1189744</v>
+        <v>1180840</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>-8904</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.75%</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4003433.9</v>
+        <v>3990128.6</v>
       </c>
     </row>
     <row r="5">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5004015</v>
+        <v>4990709.7</v>
       </c>
     </row>
     <row r="6">
@@ -935,7 +935,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.19%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -732,17 +732,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.624</v>
+        <v>4.638</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1197154</v>
+        <v>1200778</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4401</v>
+        <v>-777</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.06%</t>
         </is>
       </c>
     </row>
@@ -759,17 +759,17 @@
         <v>27.87</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>27.87</v>
+        <v>27.81</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>376245</v>
+        <v>375435</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>-810</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.22%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
         <v>33.75</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33.86</v>
+        <v>33.87</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1235890</v>
+        <v>1236255</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4015</v>
+        <v>4380</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.36%</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3990128.6</v>
+        <v>3993308.2</v>
       </c>
     </row>
     <row r="5">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4990709.7</v>
+        <v>4993889.3</v>
       </c>
     </row>
     <row r="6">
@@ -935,7 +935,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.12%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -544,12 +544,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -558,17 +558,17 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>27.87</v>
+        <v>56.12</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13500</v>
+        <v>21200</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>376245</v>
+        <v>1189744</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D2026090801</t>
+          <t>D2026090703</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -599,17 +599,17 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>56.12</v>
+        <v>33.75</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>21200</v>
+        <v>36500</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1189744</v>
+        <v>1231875</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>D2026090703</t>
+          <t>D2026090702</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -621,41 +621,82 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>600900</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>27.839</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>375826.5</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>D2026090801</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>紫金矿业</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>601899</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>36500</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1231875</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>D2026090702</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>18200</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>616252</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>D20260909M01</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -732,98 +773,98 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.638</v>
+        <v>4.629</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1200778</v>
+        <v>1198448</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-777</v>
+        <v>-3107</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>13500</v>
+        <v>21200</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>27.87</v>
+        <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>27.81</v>
+        <v>56.42</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>375435</v>
+        <v>1196104</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-810</v>
+        <v>6360</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.53%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>21200</v>
+        <v>18300</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>56.12</v>
+        <v>33.75</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>55.7</v>
+        <v>34.01</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1180840</v>
+        <v>622383</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-8904</v>
+        <v>4758</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>+0.77%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>36500</v>
+        <v>13500</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>33.75</v>
+        <v>27.839</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33.87</v>
+        <v>27.95</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1236255</v>
+        <v>377325</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4380</v>
+        <v>1499</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.40%</t>
         </is>
       </c>
     </row>
@@ -838,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -855,6 +896,16 @@
         <is>
           <t>已实现盈亏(元)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2002</v>
       </c>
     </row>
   </sheetData>
@@ -904,7 +955,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1000581.1</v>
+        <v>1617251.6</v>
       </c>
     </row>
     <row r="4">
@@ -914,7 +965,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3993308.2</v>
+        <v>3394260.1</v>
       </c>
     </row>
     <row r="5">
@@ -924,7 +975,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4993889.3</v>
+        <v>5011511.7</v>
       </c>
     </row>
     <row r="6">
@@ -935,7 +986,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.23%</t>
         </is>
       </c>
     </row>
@@ -946,7 +997,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>999.85</v>
+        <v>1461.94</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -677,24 +677,65 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>16700</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>574480</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>D2026090901</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>33.86</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>18200</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>616252</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>D20260909M01</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -773,17 +814,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.629</v>
+        <v>4.637</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1198448</v>
+        <v>1200519</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3107</v>
+        <v>-1036</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.09%</t>
         </is>
       </c>
     </row>
@@ -800,17 +841,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>56.42</v>
+        <v>56.26</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1196104</v>
+        <v>1192712</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6360</v>
+        <v>2968</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.25%</t>
         </is>
       </c>
     </row>
@@ -821,23 +862,23 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>18300</v>
+        <v>35000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>33.75</v>
+        <v>33.954</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34.01</v>
+        <v>34.4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>622383</v>
+        <v>1204000</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4758</v>
+        <v>15609</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>+1.31%</t>
         </is>
       </c>
     </row>
@@ -854,17 +895,17 @@
         <v>27.839</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>27.95</v>
+        <v>28.05</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>377325</v>
+        <v>378675</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1499</v>
+        <v>2849</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.76%</t>
         </is>
       </c>
     </row>
@@ -905,7 +946,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2002</v>
+        <v>-1712</v>
       </c>
     </row>
   </sheetData>
@@ -955,7 +996,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1617251.6</v>
+        <v>1042771.6</v>
       </c>
     </row>
     <row r="4">
@@ -965,7 +1006,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3394260.1</v>
+        <v>3975906.3</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +1016,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5011511.7</v>
+        <v>5018677.9</v>
       </c>
     </row>
     <row r="6">
@@ -986,7 +1027,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.37%</t>
         </is>
       </c>
     </row>
@@ -997,7 +1038,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1461.94</v>
+        <v>1605.56</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -677,65 +677,229 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34.4</v>
+        <v>33.86</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>16700</v>
+        <v>18200</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>574480</v>
+        <v>616252</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>D2026090901</t>
+          <t>D20260909M01</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>美的集团</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>000333</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>85.87</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>42935</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M03</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>美的集团</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>000333</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>85.86</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>386370</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M03</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>600900</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>140050</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M02</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>紫金矿业</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>601899</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>18200</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>616252</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>D20260909M01</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>16700</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>569804</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>D2026090901</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>新集能源</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>601918</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>52400</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M01</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -752,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -814,17 +978,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.637</v>
+        <v>4.617</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1200519</v>
+        <v>1195341</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1036</v>
+        <v>-6214</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.52%</t>
         </is>
       </c>
     </row>
@@ -841,17 +1005,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>56.26</v>
+        <v>55.52</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1192712</v>
+        <v>1177024</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2968</v>
+        <v>-12720</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-1.07%</t>
         </is>
       </c>
     </row>
@@ -865,20 +1029,20 @@
         <v>35000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>33.954</v>
+        <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34.4</v>
+        <v>34.11</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1204000</v>
+        <v>1193850</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15609</v>
+        <v>6421</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>+0.54%</t>
         </is>
       </c>
     </row>
@@ -889,23 +1053,77 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13500</v>
+        <v>18500</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>27.839</v>
+        <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.05</v>
+        <v>28.09</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>378675</v>
+        <v>519665</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2849</v>
+        <v>3789</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+0.73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>美的集团</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>85.861</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>431000</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1695</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>新集能源</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>52400</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -946,7 +1164,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-1712</v>
+        <v>2002</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1214,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1042771.6</v>
+        <v>425692.6</v>
       </c>
     </row>
     <row r="4">
@@ -1006,7 +1224,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3975906.3</v>
+        <v>4569280.3</v>
       </c>
     </row>
     <row r="5">
@@ -1016,7 +1234,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5018677.9</v>
+        <v>4994972.9</v>
       </c>
     </row>
     <row r="6">
@@ -1027,7 +1245,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-0.10%</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1256,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1605.56</v>
+        <v>1759.83</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -978,17 +978,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.617</v>
+        <v>4.562</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1195341</v>
+        <v>1181102</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-6214</v>
+        <v>-20453</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-1.70%</t>
         </is>
       </c>
     </row>
@@ -1005,17 +1005,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>55.52</v>
+        <v>54.63</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1177024</v>
+        <v>1158156</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-12720</v>
+        <v>-31588</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>-2.66%</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
         <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34.11</v>
+        <v>31.96</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1193850</v>
+        <v>1118600</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6421</v>
+        <v>-68829</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>-5.80%</t>
         </is>
       </c>
     </row>
@@ -1059,17 +1059,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.09</v>
+        <v>28.31</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>519665</v>
+        <v>523735</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3789</v>
+        <v>7859</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+1.52%</t>
         </is>
       </c>
     </row>
@@ -1086,17 +1086,17 @@
         <v>85.861</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>86.2</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>431000</v>
+        <v>431300</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1695</v>
+        <v>1995</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.46%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4569280.3</v>
+        <v>4465292.8</v>
       </c>
     </row>
     <row r="5">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4994972.9</v>
+        <v>4890985.4</v>
       </c>
     </row>
     <row r="6">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-2.18%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -790,31 +790,31 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>28.01</v>
+        <v>86.19</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>5000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>140050</v>
+        <v>430950</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>D20260910M02</t>
+          <t>D20260910M04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -845,17 +845,17 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34.12</v>
+        <v>28.01</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>16700</v>
+        <v>5000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>569804</v>
+        <v>140050</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>D2026090901</t>
+          <t>D20260910M02</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -872,34 +872,239 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>600900</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>258428</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M05</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>16700</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>569804</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>D2026090901</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>新集能源</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>601918</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>买入</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>10.48</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>52400</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>D20260910M01</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>新集能源</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>601918</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>146580</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M06</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>恺英网络</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>002517</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>175200</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>D20260911M02</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>8700</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>275007</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>D20260911M01</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -978,17 +1183,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.562</v>
+        <v>4.579</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1181102</v>
+        <v>1185503</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-20453</v>
+        <v>-16052</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-1.34%</t>
         </is>
       </c>
     </row>
@@ -1005,17 +1210,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>54.63</v>
+        <v>54.83</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1158156</v>
+        <v>1162396</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-31588</v>
+        <v>-27348</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>-2.30%</t>
         </is>
       </c>
     </row>
@@ -1026,23 +1231,23 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>35000</v>
+        <v>26300</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>31.96</v>
+        <v>32.26</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1118600</v>
+        <v>848438</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-68829</v>
+        <v>-43830</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-5.80%</t>
+          <t>-4.91%</t>
         </is>
       </c>
     </row>
@@ -1053,70 +1258,70 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>18500</v>
+        <v>9300</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.31</v>
+        <v>28.45</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>523735</v>
+        <v>264585</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>7859</v>
+        <v>5252</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+2.03%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>新集能源</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5000</v>
+        <v>19000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>85.861</v>
+        <v>10.473</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>86.26000000000001</v>
+        <v>10.47263157894737</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>431300</v>
+        <v>198980</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1995</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>新集能源</t>
+          <t>恺英网络</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>10.48</v>
+        <v>17.52</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10.48</v>
+        <v>17.52</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>52400</v>
+        <v>175200</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1138,7 +1343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1369,27 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2002</v>
+        <v>-18152</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>000333</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>600900</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1884</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +1439,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>425692.6</v>
+        <v>1068297.6</v>
       </c>
     </row>
     <row r="4">
@@ -1224,7 +1449,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4465292.8</v>
+        <v>3835102.1</v>
       </c>
     </row>
     <row r="5">
@@ -1234,7 +1459,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4890985.4</v>
+        <v>4903399.7</v>
       </c>
     </row>
     <row r="6">
@@ -1245,7 +1470,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>-1.93%</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1481,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1759.83</v>
+        <v>2563.56</v>
       </c>
     </row>
   </sheetData>
